--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T04:38:57+00:00</t>
+    <t>2023-05-04T06:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T06:27:52+00:00</t>
+    <t>2023-05-05T18:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:20+00:00</t>
+    <t>2023-05-05T18:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:27:53+00:00</t>
+    <t>2023-05-05T20:52:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:52:16+00:00</t>
+    <t>2023-05-06T12:19:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:19:14+00:00</t>
+    <t>2023-05-07T12:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:14:35+00:00</t>
+    <t>2023-05-07T13:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:36:00+00:00</t>
+    <t>2023-05-08T07:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T07:05:14+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>VSReasonSForARVRegimenChange</t>
+    <t>VSReasonsForARVRegimenChange</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:08:01+00:00</t>
+    <t>2023-05-11T19:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -302,7 +302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -391,37 +391,45 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B15" t="s" s="2">
+      <c r="B16" t="s" s="2">
         <v>27</v>
       </c>
     </row>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
+++ b/branches/master/ValueSet-vs-reason-arv-regimen-change.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
